--- a/data/semanas/325_pe.xlsx
+++ b/data/semanas/325_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4077,7 +4077,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17654690</v>
+        <v>17672910</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4086,22 +4086,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA - PE</t>
+          <t>439 - BOSQUE CARANDÁ PE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua PEDRO ANGELO DA ROSA</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>81 - 6 - OU</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25/09/2026 08:34</t>
+          <t>25/09/2026 08:08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25/09/2026 09:09</t>
+          <t>25/09/2026 08:26</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -4138,13 +4138,13 @@
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>46290.35694444444</v>
+        <v>46290.33888888889</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>46290.38125</v>
+        <v>46290.35138888889</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>46290</v>
@@ -4159,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>82080</v>
+        <v>80520</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>8</v>
       </c>
       <c r="AF27" t="n">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17654691</v>
+        <v>17654690</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4224,22 +4224,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>421 - IPANEMA - PE</t>
+          <t>434 - VILA AUREA - PE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua JORGE ROBERTO SALOMAO</t>
+          <t>Rua PEDRO ANGELO DA ROSA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01 - OU</t>
+          <t>81 - 6 - OU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25/09/2026 09:16</t>
+          <t>25/09/2026 08:34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25/09/2026 09:39</t>
+          <t>25/09/2026 09:09</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -4276,13 +4276,13 @@
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>46290.38611111111</v>
+        <v>46290.35694444444</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>46290.40208333333</v>
+        <v>46290.38125</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>46290</v>
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="b">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2520</v>
+        <v>1560</v>
       </c>
       <c r="AB28" t="b">
         <v>0</v>
@@ -4325,10 +4325,10 @@
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF28" t="n">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>17654692</v>
+        <v>17654691</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4362,22 +4362,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS - PE</t>
+          <t>421 - IPANEMA - PE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua JORGE ROBERTO SALOMAO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>240 - C</t>
+          <t>01 - OU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25/09/2026 09:44</t>
+          <t>25/09/2026 09:16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25/09/2026 09:59</t>
+          <t>25/09/2026 09:39</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>46290.40555555555</v>
+        <v>46290.38611111111</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46290.41597222222</v>
+        <v>46290.40208333333</v>
       </c>
       <c r="P29" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>46290</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="b">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1680</v>
+        <v>2520</v>
       </c>
       <c r="AB29" t="b">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         <v>9</v>
       </c>
       <c r="AF29" t="n">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -4486,6 +4486,144 @@
         <v>1</v>
       </c>
       <c r="AL29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17654692</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rua 18 DE JULHO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>240 - C</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:59</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46290.40555555555</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>46290.41597222222</v>
+      </c>
+      <c r="P30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R30" t="n">
+        <v>325</v>
+      </c>
+      <c r="S30" t="n">
+        <v>38</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>584</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="b">
         <v>0</v>
       </c>
     </row>
